--- a/public/documents/pieces-reponse-1/R1-menu-demi-lune-conversions.xlsx
+++ b/public/documents/pieces-reponse-1/R1-menu-demi-lune-conversions.xlsx
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -94,6 +94,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -472,14 +476,15 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menu Demi Lune : conversions au forfait identifiees dans la caisse (61 notes, 6 728,49 € encaisses). Ecart maximal constate : 0,01 €.</t>
+          <t>Menu Demi Lune : conversions au forfait identifiees dans la caisse (61 notes, 151 unites de Menu Demi Lune, 149 couverts, 6 728,49 € encaisses). Ecart maximal constate : 0,01 €.</t>
         </is>
       </c>
     </row>
@@ -543,10 +548,15 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>Unites de Menu Demi Lune</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>Composition de la note</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Ecart (€)</t>
         </is>
@@ -595,12 +605,15 @@
       <c r="J4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 15,20 €</t>
         </is>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="M4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -647,12 +660,15 @@
       <c r="J5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 49,20 €</t>
         </is>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="M5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -699,12 +715,15 @@
       <c r="J6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 27,20 €</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="M6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -751,12 +770,15 @@
       <c r="J7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>5 x Menu 'Demi Lune' a 37,42 €</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="M7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -803,12 +825,15 @@
       <c r="J8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 39,80 €</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="M8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -855,12 +880,15 @@
       <c r="J9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 38,30 €</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="M9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -907,12 +935,15 @@
       <c r="J10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 54,10 €</t>
         </is>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="M10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -959,12 +990,15 @@
       <c r="J11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 22,80 €</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="M11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1011,12 +1045,15 @@
       <c r="J12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 32,60 €</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="M12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1063,12 +1100,15 @@
       <c r="J13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 21,90 €</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="M13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1115,12 +1155,15 @@
       <c r="J14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 38,45 €</t>
         </is>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="M14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1167,12 +1210,15 @@
       <c r="J15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>4 x Menu 'Demi Lune' a 51,75 €</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1219,12 +1265,15 @@
       <c r="J16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>6 x Menu 'Demi Lune' a 31,05 €</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="M16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1271,12 +1320,15 @@
       <c r="J17" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 41,10 €</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="M17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1323,12 +1375,15 @@
       <c r="J18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 39,20 €</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="M18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1375,12 +1430,15 @@
       <c r="J19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 64,00 € + 1 x Menu 'Demi Lune' a 66,30 €</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="M19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1427,12 +1485,15 @@
       <c r="J20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 38,00 €</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="M20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1479,12 +1540,15 @@
       <c r="J21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>3 x Menu 'Demi Lune' a 32,70 €</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="M21" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1531,12 +1595,15 @@
       <c r="J22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 45,05 €</t>
         </is>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="M22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1583,12 +1650,15 @@
       <c r="J23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 32,40 €</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="M23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1635,12 +1705,15 @@
       <c r="J24" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 37,30 €</t>
         </is>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1687,12 +1760,15 @@
       <c r="J25" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 52,00 €</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="M25" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1739,12 +1815,15 @@
       <c r="J26" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>4 x Menu 'Demi Lune' a 50,95 €</t>
         </is>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="M26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1791,12 +1870,15 @@
       <c r="J27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 35,80 €</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="M27" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1843,12 +1925,15 @@
       <c r="J28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 30,30 €</t>
         </is>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="M28" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1895,12 +1980,15 @@
       <c r="J29" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 64,40 €</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1947,12 +2035,15 @@
       <c r="J30" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>5 x Menu 'Demi Lune' a 41,70 €</t>
         </is>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1999,12 +2090,15 @@
       <c r="J31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 32,30 €</t>
         </is>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2051,12 +2145,15 @@
       <c r="J32" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>7 x Menu 'Demi Lune' a 35,40 €</t>
         </is>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="M32" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2103,12 +2200,15 @@
       <c r="J33" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>5 x Menu 'Demi Lune' a 32,38 €</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="M33" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2155,12 +2255,15 @@
       <c r="J34" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 45,40 €</t>
         </is>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="M34" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2207,12 +2310,15 @@
       <c r="J35" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="K35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 39,65 €</t>
         </is>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="M35" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2259,12 +2365,15 @@
       <c r="J36" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 45,05 € + 2 x Menu Bourguignon a 44,00 €</t>
         </is>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="M36" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2311,12 +2420,15 @@
       <c r="J37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 51,15 €</t>
         </is>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2363,12 +2475,15 @@
       <c r="J38" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>8 x Menu 'Demi Lune' a 49,00 € + 1 x Menu Franc-Comtois a 41,30 €</t>
         </is>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="M38" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2415,12 +2530,15 @@
       <c r="J39" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 24,35 €</t>
         </is>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="M39" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2467,12 +2585,15 @@
       <c r="J40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>2 x FORMULE EXPRESS a 23,50 € + 1 x Menu 'Demi Lune' a 23,60 €</t>
         </is>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="M40" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2519,12 +2640,15 @@
       <c r="J41" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 41,35 €</t>
         </is>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="M41" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2571,12 +2695,15 @@
       <c r="J42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 30,30 €</t>
         </is>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="M42" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2623,12 +2750,15 @@
       <c r="J43" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 55,00 € + 1 x Menu Franc-Comtois a 48,20 €</t>
         </is>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="M43" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2675,12 +2805,15 @@
       <c r="J44" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="K44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 30,65 €</t>
         </is>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="M44" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2727,12 +2860,15 @@
       <c r="J45" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 44,65 €</t>
         </is>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="M45" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2779,12 +2915,15 @@
       <c r="J46" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 33,30 €</t>
         </is>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="M46" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2831,12 +2970,15 @@
       <c r="J47" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 54,35 €</t>
         </is>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="M47" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2883,12 +3025,15 @@
       <c r="J48" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 64,85 €</t>
         </is>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="M48" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2935,12 +3080,15 @@
       <c r="J49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 30,90 €</t>
         </is>
       </c>
-      <c r="L49" s="4" t="n">
+      <c r="M49" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2987,12 +3135,15 @@
       <c r="J50" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 67,25 €</t>
         </is>
       </c>
-      <c r="L50" s="4" t="n">
+      <c r="M50" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3039,12 +3190,15 @@
       <c r="J51" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="K51" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 32,60 €</t>
         </is>
       </c>
-      <c r="L51" s="4" t="n">
+      <c r="M51" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3091,12 +3245,15 @@
       <c r="J52" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>4 x Menu 'Demi Lune' a 45,55 €</t>
         </is>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="M52" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3143,12 +3300,15 @@
       <c r="J53" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 21,60 €</t>
         </is>
       </c>
-      <c r="L53" s="4" t="n">
+      <c r="M53" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3195,12 +3355,15 @@
       <c r="J54" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K54" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 51,50 €</t>
         </is>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="M54" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3247,12 +3410,15 @@
       <c r="J55" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>3 x Menu 'Demi Lune' a 28,63 €</t>
         </is>
       </c>
-      <c r="L55" s="4" t="n">
+      <c r="M55" s="4" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -3299,12 +3465,15 @@
       <c r="J56" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K56" s="5" t="inlineStr">
+      <c r="K56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>3 x Menu 'Demi Lune' a 50,00 € + 4 x Menu du jour a 42,60 €</t>
         </is>
       </c>
-      <c r="L56" s="4" t="n">
+      <c r="M56" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,12 +3520,15 @@
       <c r="J57" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K57" s="5" t="inlineStr">
+      <c r="K57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 57,95 €</t>
         </is>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="M57" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3403,12 +3575,15 @@
       <c r="J58" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="K58" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 50,00 € + 1 x Menu du jour a 57,30 €</t>
         </is>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="M58" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3455,12 +3630,15 @@
       <c r="J59" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K59" s="5" t="inlineStr">
+      <c r="K59" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>5 x Menu 'Demi Lune' a 48,68 €</t>
         </is>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="M59" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3507,12 +3685,15 @@
       <c r="J60" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K60" s="5" t="inlineStr">
+      <c r="K60" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 29,20 €</t>
         </is>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="M60" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3559,12 +3740,15 @@
       <c r="J61" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K61" s="5" t="inlineStr">
+      <c r="K61" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 25,70 €</t>
         </is>
       </c>
-      <c r="L61" s="4" t="n">
+      <c r="M61" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3611,12 +3795,15 @@
       <c r="J62" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K62" s="5" t="inlineStr">
+      <c r="K62" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>3 x Menu 'Demi Lune' a 50,00 € + 1 x Menu 'Demi Lune' a 52,10 €</t>
         </is>
       </c>
-      <c r="L62" s="4" t="n">
+      <c r="M62" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3663,12 +3850,15 @@
       <c r="J63" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K63" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>2 x Menu 'Demi Lune' a 66,80 €</t>
         </is>
       </c>
-      <c r="L63" s="4" t="n">
+      <c r="M63" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3715,12 +3905,15 @@
       <c r="J64" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="K64" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>1 x Menu 'Demi Lune' a 37,20 €</t>
         </is>
       </c>
-      <c r="L64" s="4" t="n">
+      <c r="M64" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3736,7 +3929,7 @@
         <v>421</v>
       </c>
       <c r="E65" s="6" t="n">
-        <v>6728.49</v>
+        <v>6728.5</v>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
       <c r="G65" s="6" t="inlineStr"/>
@@ -3747,15 +3940,42 @@
       <c r="J65" s="6" t="n">
         <v>149</v>
       </c>
-      <c r="K65" s="6" t="inlineStr"/>
-      <c r="L65" s="6" t="n">
-        <v>0</v>
+      <c r="K65" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="L65" s="6" t="inlineStr"/>
+      <c r="M65" s="7" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Lecture des deux colonnes de quantite : la colonne « Couverts » ne retient que la quantite de la PREMIERE ligne « Menu Demi Lune » de la note ; la colonne « Unites de Menu Demi Lune » somme toutes ces lignes. Les deux totaux different de 2 unite(s), du seul fait des 2 note(s) ou le forfait a ete saisi en deux lignes a des prix differents : 2023-03-22 (note 12), 2024-12-11 (note 18). Total general : 151 unites de Menu Demi Lune pour 149 couverts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Lecture de la colonne « Ecart » : somme des lignes supprimees (6 728,50 €) moins total des notes encaissees (6 728,49 €), soit 0,01 € cumules sur les 61 conversions. Cet ecart provient d'une seule note, ou la division du total par le nombre de couverts ne tombe pas juste au centime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Taux de couverture : ces 151 unites de Menu Demi Lune se rapportent aux 332 Menus Demi Lune vendus hors catalogue que denombre l'onglet « Dispersion par periode », soit 45,5 %.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A68:M68"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A67:M67"/>
+    <mergeCell ref="A69:M69"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
